--- a/data/trans_dic/P1419-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P1419-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,67; 4,11</t>
+          <t>1,69; 4,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,95</t>
+          <t>0,83; 3,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,66</t>
+          <t>0,7; 2,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,57; 5,57</t>
+          <t>2,63; 5,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,98; 9,98</t>
+          <t>5,92; 9,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,72; 11,24</t>
+          <t>6,56; 11,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,0; 6,34</t>
+          <t>3,07; 6,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,09; 13,74</t>
+          <t>9,81; 13,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,17; 6,5</t>
+          <t>4,28; 6,64</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,16; 6,57</t>
+          <t>4,13; 6,54</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,13; 3,99</t>
+          <t>2,17; 4,08</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,86; 9,27</t>
+          <t>6,75; 9,17</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,96; 4,3</t>
+          <t>1,9; 4,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,89</t>
+          <t>0,56; 1,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,63</t>
+          <t>0,4; 1,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,12; 3,41</t>
+          <t>2,16; 4,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,94; 13,12</t>
+          <t>8,78; 13,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,28; 11,03</t>
+          <t>7,23; 11,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,79; 9,32</t>
+          <t>5,84; 9,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,43; 12,43</t>
+          <t>9,26; 12,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,73; 8,12</t>
+          <t>5,83; 8,2</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,24; 6,36</t>
+          <t>4,27; 6,33</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,3; 5,25</t>
+          <t>3,22; 5,37</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,89; 7,27</t>
+          <t>6,05; 7,86</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,08; 5,12</t>
+          <t>2,08; 4,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,2</t>
+          <t>0,41; 2,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,55</t>
+          <t>0,85; 2,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,14; 6,19</t>
+          <t>3,22; 6,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,34; 14,35</t>
+          <t>9,1; 14,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,91; 10,09</t>
+          <t>5,95; 10,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,99; 5,83</t>
+          <t>3,0; 6,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,99; 11,65</t>
+          <t>9,65; 13,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,09; 8,81</t>
+          <t>5,97; 8,87</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,56; 5,82</t>
+          <t>3,53; 5,78</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,05; 3,89</t>
+          <t>2,11; 3,93</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,36; 8,06</t>
+          <t>6,95; 9,36</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,22; 4,44</t>
+          <t>2,31; 4,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,12</t>
+          <t>0,53; 2,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,65</t>
+          <t>1,53; 3,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,14; 5,6</t>
+          <t>2,94; 5,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,06; 14,31</t>
+          <t>10,23; 14,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,33; 9,64</t>
+          <t>6,44; 9,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,73; 9,17</t>
+          <t>5,84; 9,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,59; 11,12</t>
+          <t>8,88; 11,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,77; 9,1</t>
+          <t>6,72; 9,24</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,81; 5,73</t>
+          <t>3,74; 5,63</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,07; 6,09</t>
+          <t>3,98; 6,19</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,07; 8,19</t>
+          <t>6,41; 8,31</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,45; 3,64</t>
+          <t>2,44; 3,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,64</t>
+          <t>0,85; 1,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,17; 1,97</t>
+          <t>1,15; 2,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,71; 4,21</t>
+          <t>3,26; 4,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,8; 11,92</t>
+          <t>9,68; 11,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,55; 9,48</t>
+          <t>7,55; 9,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,29; 7,08</t>
+          <t>5,34; 7,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,23; 11,15</t>
+          <t>10,17; 11,77</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,37; 7,6</t>
+          <t>6,3; 7,57</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,32; 5,39</t>
+          <t>4,39; 5,43</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,44; 4,43</t>
+          <t>3,4; 4,4</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,03; 7,57</t>
+          <t>6,91; 7,97</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24473</t>
+          <t>27040</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>79518</t>
+          <t>85014</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>103991</t>
+          <t>112054</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11608; 28503</t>
+          <t>11696; 28668</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5512; 20749</t>
+          <t>5859; 22064</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4603; 17947</t>
+          <t>4739; 17585</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16326; 35376</t>
+          <t>18160; 39116</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>41172; 68700</t>
+          <t>40718; 68548</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>46809; 78321</t>
+          <t>45761; 77109</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20215; 42659</t>
+          <t>20649; 43301</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>68144; 92828</t>
+          <t>71897; 99965</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>57650; 89877</t>
+          <t>59209; 91731</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58286; 92010</t>
+          <t>57837; 91569</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28650; 53826</t>
+          <t>29270; 54932</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>89986; 121453</t>
+          <t>96108; 130533</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27534</t>
+          <t>31516</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>103913</t>
+          <t>114014</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>131447</t>
+          <t>145529</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18836; 41364</t>
+          <t>18306; 41791</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5420; 19246</t>
+          <t>5686; 19612</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3981; 16671</t>
+          <t>4081; 15807</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13392; 40685</t>
+          <t>22605; 43504</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>86598; 127069</t>
+          <t>85060; 126799</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>74860; 113533</t>
+          <t>74380; 113643</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>60338; 97162</t>
+          <t>60942; 97898</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>90177; 118930</t>
+          <t>99087; 130494</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>110550; 156757</t>
+          <t>112593; 158224</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>86720; 130197</t>
+          <t>87494; 129658</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>68218; 108377</t>
+          <t>66559; 110862</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>83522; 156267</t>
+          <t>128121; 166612</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30118</t>
+          <t>35840</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>79102</t>
+          <t>93696</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>109220</t>
+          <t>129536</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14121; 34756</t>
+          <t>14089; 33566</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3858; 16684</t>
+          <t>3080; 17453</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6506; 19385</t>
+          <t>6478; 20214</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22062; 43510</t>
+          <t>25789; 49000</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>63858; 98138</t>
+          <t>62223; 95915</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>45908; 78449</t>
+          <t>46236; 78936</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23452; 45794</t>
+          <t>23544; 48398</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>37201; 108701</t>
+          <t>78297; 108403</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>82931; 119982</t>
+          <t>81385; 120850</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>54679; 89329</t>
+          <t>54159; 88705</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31718; 60141</t>
+          <t>32573; 60712</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>71350; 131814</t>
+          <t>112143; 150881</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>39748</t>
+          <t>40864</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>103843</t>
+          <t>113612</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>143591</t>
+          <t>154476</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20915; 41817</t>
+          <t>21742; 42912</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4956; 20067</t>
+          <t>5004; 19675</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13952; 34242</t>
+          <t>14301; 34693</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29087; 51860</t>
+          <t>29083; 52439</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>104461; 148635</t>
+          <t>106201; 149226</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>66631; 101358</t>
+          <t>67752; 102424</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>59807; 95692</t>
+          <t>61007; 96939</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>82839; 121459</t>
+          <t>99226; 132558</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>134187; 180353</t>
+          <t>133142; 183007</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>76142; 114526</t>
+          <t>74832; 112653</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>80582; 120609</t>
+          <t>78929; 122622</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>122573; 165253</t>
+          <t>135159; 175135</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>121874</t>
+          <t>135259</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>366375</t>
+          <t>406336</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>488249</t>
+          <t>541595</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>80228; 119234</t>
+          <t>79996; 120579</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>28211; 56092</t>
+          <t>29023; 57158</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>39723; 66907</t>
+          <t>39141; 69582</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>93768; 145705</t>
+          <t>115239; 157044</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>331117; 402712</t>
+          <t>326983; 400540</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>268434; 337083</t>
+          <t>268396; 331839</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>187489; 251019</t>
+          <t>189281; 249845</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>301167; 407814</t>
+          <t>379438; 439184</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>424119; 505612</t>
+          <t>419464; 503578</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>301477; 376641</t>
+          <t>306249; 379222</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>238950; 307574</t>
+          <t>235967; 305143</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>428811; 538558</t>
+          <t>501568; 578599</t>
         </is>
       </c>
     </row>
